--- a/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:50:27+00:00</t>
+    <t>2026-04-07T13:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:39:53+00:00</t>
+    <t>2026-04-08T09:43:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4710,7 +4710,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>167</v>
       </c>
@@ -4729,7 +4729,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -5114,7 +5114,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>177</v>
       </c>
@@ -5129,13 +5129,13 @@
         <v>62</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5217,7 +5217,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>181</v>
       </c>
@@ -5232,13 +5232,13 @@
         <v>182</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>74</v>
@@ -5526,7 +5526,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>195</v>
       </c>
@@ -5547,7 +5547,7 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
